--- a/Writing/week2/week2.xlsx
+++ b/Writing/week2/week2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yashkarle/soccer-ds-stats/Writing/week2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68E82AA6-36FF-E445-8932-7FEF370FEB1F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBC6D76F-7D16-BE43-A9C6-A75AEC97B591}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19040" activeTab="2" xr2:uid="{E93522CD-A16F-944B-B80D-1F57AE0445AA}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19040" activeTab="1" xr2:uid="{E93522CD-A16F-944B-B80D-1F57AE0445AA}"/>
   </bookViews>
   <sheets>
     <sheet name="1 Match Analysis" sheetId="1" r:id="rId1"/>
